--- a/src/main/java/com/awinas/learning/leetcode/DSA_NOTES.xlsx
+++ b/src/main/java/com/awinas/learning/leetcode/DSA_NOTES.xlsx
@@ -1,22 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/a0m0rtj/AwinasKannan/Official/LearningRepos/Java-Features/src/main/java/com/awinas/learning/leetcode/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C0470E1-E491-8749-BD3B-69C10F1B3887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C94EDF7E-F9E7-F340-9F93-326241204BC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="21600" xr2:uid="{D5756C59-A993-0448-8F9C-A2EBCDD5D59F}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="5" xr2:uid="{D5756C59-A993-0448-8F9C-A2EBCDD5D59F}"/>
   </bookViews>
   <sheets>
     <sheet name="Two Pointers" sheetId="2" r:id="rId1"/>
     <sheet name="Sliding Window" sheetId="3" r:id="rId2"/>
     <sheet name="Trees" sheetId="1" r:id="rId3"/>
     <sheet name="Linked List" sheetId="4" r:id="rId4"/>
+    <sheet name="Graph" sheetId="5" r:id="rId5"/>
+    <sheet name="BFS DFS" sheetId="6" r:id="rId6"/>
+    <sheet name="NOTES" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Trees!$A$1:$H$2</definedName>
@@ -42,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="108">
   <si>
     <t>No</t>
   </si>
@@ -577,12 +580,212 @@
   <si>
     <t xml:space="preserve">Binary Tree </t>
   </si>
+  <si>
+    <t>200. Number of Islands</t>
+  </si>
+  <si>
+    <t>Visit Down , UP  Rows . Left , Right Cols.
+Either use separate Visited arr or use the exiting grid and mark the visited as 0.
+Count the Island before the dfs itself
+Comparison
+- Traversal Method:
+  DFS → Recursion / Stack
+  BFS → Queue
+- Visits Each Cell:
+  DFS → Once
+  BFS → Once
+- Risk:
+  DFS → StackOverflowError possible on very large grids
+  BFS → No recursion, so no StackOverflowError
+- Interview:
+  DFS → Shorter and most commonly expected
+  BFS → Equally correct; preferred for very large grids</t>
+  </si>
+  <si>
+    <t>DFS vs BFS (Number of Islands)
+Time Complexity
+- DFS: O(m × n)
+- BFS: O(m × n)
+Space Complexity
+- DFS:
+  • Visited Array = O(m × n)
+  • Recursion Stack (Worst Case) = O(m × n)
+  • Total = O(m × n)
+- BFS:
+  • Visited Array = O(m × n)
+  • Queue (Worst Case) = O(m × n)
+  • Total = O(m × n)</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>733. Flood Fill</t>
+  </si>
+  <si>
+    <t>DFS  , MATRIX TREAVERSAL</t>
+  </si>
+  <si>
+    <t>Every cell is processed at most once.
+DFS stores cells in the recursion stack.
+BFS stores cells in the queue.
+No extra visited[][] array is required because the image itself is updated.</t>
+  </si>
+  <si>
+    <t>DFS 
+Time  : O(m × n)
+Space : O(m × n)   // Recursion Stack
+BFS (Check Repo)
+-----
+Time  : O(m × n)
+Space : O(m × n)   // Queue</t>
+  </si>
+  <si>
+    <t>130. Surrounded Regions</t>
+  </si>
+  <si>
+    <t>Traverse only the boundary cells. Whenever a boundary cell contains 'O', 
+perform DFS (or BFS) to mark all connected 'O' cells as safe (e.g., mark them as 'T').
+After all boundary cells have been processed, 
+traverse the entire board and convert the remaining 'O' cells to 'X', then change all 'T' cells back to 'O'.</t>
+  </si>
+  <si>
+    <t>1. Traverse all boundary cells.
+2. If boundary cell == 'O'
+      DFS/BFS
+      Mark all connected O's as 'T' (Safe)
+3. Traverse the entire board
+      O -&gt; X    // Surrounded region
+      T -&gt; O    // Restore safe region</t>
+  </si>
+  <si>
+    <t>DFS
+----
+Time  : O(m × n)
+Space : O(m × n)   // Recursion Stack
+Reason:
+- Traverse all boundary cells.
+- DFS marks each 'O' at most once.
+- Final traversal flips O -&gt; X and T -&gt; O.
+BFS
+----
+Time  : O(m × n)
+Space : O(m × n)   // Queue
+BFS
+----
+Time  : O(m × n)
+Space : O(m × n)   // Queue</t>
+  </si>
+  <si>
+    <t>994. Rotting Oranges</t>
+  </si>
+  <si>
+    <t>Time  : O(m × n)
+Space : O(m × n)   // Queue
+Reason:
+- Initial traversal = O(m × n)
+- Every orange is added to the queue at most once.
+- Every orange is processed at most once.
+- No visited[][] array is needed because a fresh orange (1) is immediately marked rotten (2).</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>// BFS - One level = One minute</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Approach:
+1. Traverse the grid.
+2. Count all fresh oranges.
+3. Add all rotten oranges to the queue.
+4. Perform BFS level by level.
+5. For each rotten orange, rot its 4-directional fresh neighbors.
+6. Mark newly rotten oranges as 2 and add them to the queue.
+7. Decrement freshCount.
+8. As soon as freshCount == 0, return the current minute.
+9. If BFS ends and fresh oranges still exist, return -1.</t>
+    </r>
+  </si>
+  <si>
+    <t>https://algo.monster/liteproblems/994</t>
+  </si>
+  <si>
+    <t>NOTE</t>
+  </si>
+  <si>
+    <t>The question asks:
+Return the shortest transformation sequence length.
+Whenever you see:
+Shortest path
+Minimum steps
+Minimum moves
+Minimum transformations
+in an unweighted graph, think:
+BFS</t>
+  </si>
+  <si>
+    <t>127. Word Ladder</t>
+  </si>
+  <si>
+    <t>HARD</t>
+  </si>
+  <si>
+    <t>DFS  , MATRIX TREAVERSAL , Boundary DFS</t>
+  </si>
+  <si>
+    <t>BFS  , MATRIX TREAVERSAL , Multi-Source BFS</t>
+  </si>
+  <si>
+    <t>Graph BFS (Implicit Graph)</t>
+  </si>
+  <si>
+    <t>Complexity
+Time: O(N × L × 26)
+Space: O(N)</t>
+  </si>
+  <si>
+    <t>Why BFS?
+The question asks:
+Return the shortest transformation sequence length.
+Whenever you see:
+Shortest path
+Minimum steps
+Minimum moves
+Minimum transformations
+in an unweighted graph, think:
+BFS</t>
+  </si>
+  <si>
+    <t>1. Store all words in a HashSet.
+2. Start BFS from beginWord.
+3. For each word:
+      Change one character at a time ('a' to 'z').
+4. If the new word exists in the HashSet:
+      Add it to the queue.
+      Remove it from the HashSet (visited).
+5. BFS Level = Transformation Count.
+6. When endWord is found, return the current level.
+7. If BFS finishes without finding endWord, return 0.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -624,6 +827,13 @@
       <color rgb="FFFF0000"/>
       <name val="Aptos Narrow (Body)"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -646,17 +856,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1490,7 +1701,7 @@
       <c r="G9" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="4" t="s">
         <v>60</v>
       </c>
       <c r="I9" s="2" t="s">
@@ -1559,7 +1770,7 @@
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" t="s">
         <v>69</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -1582,7 +1793,7 @@
       </c>
     </row>
     <row r="13" spans="1:9" ht="153" x14ac:dyDescent="0.2">
-      <c r="B13" s="4" t="s">
+      <c r="B13" t="s">
         <v>76</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -1605,7 +1816,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="B14" s="4" t="s">
+      <c r="B14" t="s">
         <v>80</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -1715,4 +1926,293 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBD555E4-AD4A-0D48-BEF3-DF4673E0B611}">
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="3.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D1854DA-383E-4046-8B31-1D12D4D2D8BB}">
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="3.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="38.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="114.1640625" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="44.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="356" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6">
+        <v>46204</v>
+      </c>
+      <c r="C2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="136" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6">
+        <v>46204</v>
+      </c>
+      <c r="C3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="306" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6">
+        <v>46204</v>
+      </c>
+      <c r="C4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>102</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="204" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6">
+        <v>46204</v>
+      </c>
+      <c r="C5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" t="s">
+        <v>103</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="272" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6">
+        <v>46204</v>
+      </c>
+      <c r="C6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" t="s">
+        <v>101</v>
+      </c>
+      <c r="G6" t="s">
+        <v>104</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" display="https://leetcode.com/problems/number-of-islands/" xr:uid="{B9E784F7-5C11-CA4F-A8AD-DB3FC3B5AC91}"/>
+    <hyperlink ref="D3" r:id="rId2" display="https://leetcode.com/problems/flood-fill/" xr:uid="{13D6E50B-E9CE-464A-831F-580082A31DE5}"/>
+    <hyperlink ref="D4" r:id="rId3" display="https://leetcode.com/problems/surrounded-regions/" xr:uid="{723D21A4-1930-EA42-B1E3-49CA2E03091B}"/>
+    <hyperlink ref="D5" r:id="rId4" display="https://leetcode.com/problems/rotting-oranges/" xr:uid="{C1F53BFB-87D3-3F4C-9CF1-14C06D190621}"/>
+    <hyperlink ref="J5" r:id="rId5" xr:uid="{285F8C16-401D-D541-8188-221D1501F996}"/>
+    <hyperlink ref="D6" r:id="rId6" display="https://leetcode.com/problems/word-ladder/" xr:uid="{AC2F3E93-3694-F74C-B164-2BEDAA9D21E1}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABBB2DF8-FFE8-0B45-BB91-571CE06BDF04}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="91.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="238" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/main/java/com/awinas/learning/leetcode/DSA_NOTES.xlsx
+++ b/src/main/java/com/awinas/learning/leetcode/DSA_NOTES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/a0m0rtj/AwinasKannan/Official/LearningRepos/Java-Features/src/main/java/com/awinas/learning/leetcode/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C94EDF7E-F9E7-F340-9F93-326241204BC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B02BD443-71EE-7840-8911-AEE5490F798E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="5" xr2:uid="{D5756C59-A993-0448-8F9C-A2EBCDD5D59F}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="33560" windowHeight="21600" activeTab="5" xr2:uid="{D5756C59-A993-0448-8F9C-A2EBCDD5D59F}"/>
   </bookViews>
   <sheets>
     <sheet name="Two Pointers" sheetId="2" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="110">
   <si>
     <t>No</t>
   </si>
@@ -779,6 +779,12 @@
 5. BFS Level = Transformation Count.
 6. When endWord is found, return the current level.
 7. If BFS finishes without finding endWord, return 0.</t>
+  </si>
+  <si>
+    <t>Shortest Path in an Unweighted Graph</t>
+  </si>
+  <si>
+    <t>Pattern</t>
   </si>
 </sst>
 </file>
@@ -1980,7 +1986,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D1854DA-383E-4046-8B31-1D12D4D2D8BB}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.5" bestFit="1" customWidth="1"/>
@@ -1990,11 +1996,12 @@
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="38.1640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="114.1640625" customWidth="1"/>
-    <col min="9" max="9" width="64.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="44.1640625" customWidth="1"/>
+    <col min="9" max="9" width="32" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="64.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="44.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2020,13 +2027,16 @@
         <v>22</v>
       </c>
       <c r="I1" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="356" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" ht="356" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2051,14 +2061,15 @@
       <c r="H2" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="2"/>
+      <c r="J2" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="136" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" ht="136" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2083,11 +2094,12 @@
       <c r="H3" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="2"/>
+      <c r="J3" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="306" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" ht="306" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2112,14 +2124,15 @@
       <c r="H4" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="2"/>
+      <c r="J4" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="204" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" ht="204" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2144,14 +2157,15 @@
       <c r="H5" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="2"/>
+      <c r="J5" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="272" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="272" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2177,9 +2191,12 @@
         <v>105</v>
       </c>
       <c r="I6" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>106</v>
       </c>
     </row>
@@ -2189,7 +2206,7 @@
     <hyperlink ref="D3" r:id="rId2" display="https://leetcode.com/problems/flood-fill/" xr:uid="{13D6E50B-E9CE-464A-831F-580082A31DE5}"/>
     <hyperlink ref="D4" r:id="rId3" display="https://leetcode.com/problems/surrounded-regions/" xr:uid="{723D21A4-1930-EA42-B1E3-49CA2E03091B}"/>
     <hyperlink ref="D5" r:id="rId4" display="https://leetcode.com/problems/rotting-oranges/" xr:uid="{C1F53BFB-87D3-3F4C-9CF1-14C06D190621}"/>
-    <hyperlink ref="J5" r:id="rId5" xr:uid="{285F8C16-401D-D541-8188-221D1501F996}"/>
+    <hyperlink ref="K5" r:id="rId5" xr:uid="{285F8C16-401D-D541-8188-221D1501F996}"/>
     <hyperlink ref="D6" r:id="rId6" display="https://leetcode.com/problems/word-ladder/" xr:uid="{AC2F3E93-3694-F74C-B164-2BEDAA9D21E1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/main/java/com/awinas/learning/leetcode/DSA_NOTES.xlsx
+++ b/src/main/java/com/awinas/learning/leetcode/DSA_NOTES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/a0m0rtj/AwinasKannan/Official/LearningRepos/Java-Features/src/main/java/com/awinas/learning/leetcode/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B02BD443-71EE-7840-8911-AEE5490F798E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9977DA3-14AD-0747-A712-9E897DDEB83D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="33560" windowHeight="21600" activeTab="5" xr2:uid="{D5756C59-A993-0448-8F9C-A2EBCDD5D59F}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" activeTab="2" xr2:uid="{D5756C59-A993-0448-8F9C-A2EBCDD5D59F}"/>
   </bookViews>
   <sheets>
     <sheet name="Two Pointers" sheetId="2" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="113">
   <si>
     <t>No</t>
   </si>
@@ -535,9 +535,6 @@
     <t>112. Path Sum</t>
   </si>
   <si>
-    <t>Binary Tree , DFS , BFS</t>
-  </si>
-  <si>
     <t>Recursion
 Time: O(n) → visit each node once.
 Space: O(h) → recursion depth (height of tree).</t>
@@ -578,9 +575,6 @@
     <t>113. Path Sum II</t>
   </si>
   <si>
-    <t xml:space="preserve">Binary Tree </t>
-  </si>
-  <si>
     <t>200. Number of Islands</t>
   </si>
   <si>
@@ -785,6 +779,24 @@
   </si>
   <si>
     <t>Pattern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binary Search Tree , Recursion </t>
+  </si>
+  <si>
+    <t>Binary Tree , DFS , BFS ,Pre Order</t>
+  </si>
+  <si>
+    <t>Time: O(n)
+Space: O(h) (excluding the output list)</t>
+  </si>
+  <si>
+    <t>Binary Tree ,Pre Order DFS</t>
+  </si>
+  <si>
+    <t>Path Sum 1 vs 2:
+Instead of returning  true, you save the current path and continue searching.
+Remove the last value from current path once added</t>
   </si>
 </sst>
 </file>
@@ -1789,13 +1801,16 @@
         <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>70</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>71</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="153" x14ac:dyDescent="0.2">
@@ -1812,21 +1827,24 @@
         <v>7</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="H13" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="I13" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="51" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="B14" t="s">
-        <v>80</v>
-      </c>
       <c r="C14" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D14" t="s">
         <v>6</v>
@@ -1835,7 +1853,16 @@
         <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>81</v>
+        <v>111</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -2006,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>9</v>
@@ -2027,7 +2054,7 @@
         <v>22</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>3</v>
@@ -2044,10 +2071,10 @@
         <v>46204</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -2056,14 +2083,14 @@
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I2" s="2"/>
       <c r="J2" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K2" t="s">
         <v>50</v>
@@ -2077,10 +2104,10 @@
         <v>46204</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -2089,14 +2116,14 @@
         <v>7</v>
       </c>
       <c r="G3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="306" x14ac:dyDescent="0.2">
@@ -2107,10 +2134,10 @@
         <v>46204</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -2119,17 +2146,17 @@
         <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="204" x14ac:dyDescent="0.2">
@@ -2140,10 +2167,10 @@
         <v>46204</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -2152,17 +2179,17 @@
         <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="272" x14ac:dyDescent="0.2">
@@ -2173,31 +2200,31 @@
         <v>46204</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G6" t="s">
+        <v>102</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -2223,10 +2250,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="238" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
